--- a/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T11:38:12+00:00</t>
+    <t>2026-09-13T16:44:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
+++ b/ValueSet-mii-vs-dokument-sct-dokument-typ.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T16:44:42+00:00</t>
+    <t>2026-09-14T07:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
